--- a/excel/files_08_data_analysis/examples.xlsx
+++ b/excel/files_08_data_analysis/examples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hanzenl-my.sharepoint.com/personal/j_hageman_pl_hanze_nl/Documents/web_pages/data_analysis_bml-r/data_analysis_bml/excel/files_08_data_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{3B6CB5D2-D69F-49A5-A383-7E44225A4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC9A83CC-28D2-4C10-B35D-BA805349726F}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{3B6CB5D2-D69F-49A5-A383-7E44225A4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C2A4C3-7A45-430F-94C8-B5A75CDDA92F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{EECC7863-79BC-4C52-BFCC-4F50C68B49DC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EECC7863-79BC-4C52-BFCC-4F50C68B49DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,9 +571,9 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6">
-        <f>SUM(C2:C5,D2:D5)</f>
-        <v>83.528999999999996</v>
+      <c r="E6" cm="1">
+        <f t="array" ref="E6">SUM(C2:C5*D2:D5)</f>
+        <v>11.684000000000001</v>
       </c>
     </row>
   </sheetData>
